--- a/examples/demos/05_simulation_and_charts.xlsx
+++ b/examples/demos/05_simulation_and_charts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3663E3E4-195B-4549-9DC7-A39AC377177A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B692E3D-04C6-4A84-8C36-25555FFAC609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Demo 05 — Simulate and read the results</t>
   </si>
@@ -54,22 +54,40 @@
     <t>Tools demonstrated: replace_constant_with_distribution, wrap_with_output, run_simulation, get_simulation_results, list_vmrs_variables, create_histogram_chart, create_cdf_chart, create_tornado_chart</t>
   </si>
   <si>
-    <t>PREREQUISITES</t>
-  </si>
-  <si>
-    <t>Windows Excel with the ModelRisk add-in installed and licensed.</t>
-  </si>
-  <si>
-    <t>modelrisk-mcp connected to Claude (Claude Desktop / Claude Code).</t>
-  </si>
-  <si>
-    <t>PROMPT →  Open C:/Users/timou/source/repos/modelrisk-mcp/examples/demos/05_simulation_and_charts.xlsx in Excel</t>
+    <t>GETTING STARTED</t>
+  </si>
+  <si>
+    <t>You need: Windows Excel with the ModelRisk add-in installed and licensed, and modelrisk-mcp connected to Claude (Claude Desktop or Claude Code).</t>
+  </si>
+  <si>
+    <t>Save the demo gallery folder anywhere on your PC. Once per session, tell Claude where it is and which demo to open:</t>
+  </si>
+  <si>
+    <t>PROMPT →  My ModelRisk demo gallery is in &lt;your folder, e.g. Documents\modelrisk-demos&gt;. Open 05_simulation_and_charts.xlsx from there.</t>
+  </si>
+  <si>
+    <t>Claude remembers the folder for the rest of the session — later demos just need "Open &lt;file&gt; from the demo folder".</t>
+  </si>
+  <si>
+    <t>FAST TRACK — ONE PROMPT DOES IT ALL</t>
+  </si>
+  <si>
+    <t>In a hurry? This single prompt runs the whole demo end-to-end. Prefer to learn how it works? Skip to the numbered steps below — same result, one capability at a time.</t>
+  </si>
+  <si>
+    <t>PROMPT →  In this workbook, replace Model!B6 with VosePERT(130,145,175) named UnitCost and Model!B7 with VosePERT(50,80,120) named Volume, wrap Profit B11 as output "Profit", and run 10,000 iterations with seed 1. Then give me the full statistics for Profit and create three charts: a histogram, a CDF and a tornado.</t>
+  </si>
+  <si>
+    <t>Expected: simulated results plus three native Excel chart sheets.</t>
   </si>
   <si>
     <t>STEP-BY-STEP</t>
   </si>
   <si>
     <t>Open the workbook. Look at the Model sheet: a simple deterministic profit line — price, unit cost, volume, fixed costs.</t>
+  </si>
+  <si>
+    <t>PROMPT →  Open 05_simulation_and_charts.xlsx from the demo folder.</t>
   </si>
   <si>
     <t>Expected: Excel opens the workbook; the Model sheet shows Profit ($k) of about 1,820.</t>
@@ -202,7 +220,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,6 +252,40 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
@@ -257,12 +309,32 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E4F92"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF4FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -307,36 +379,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -643,7 +721,7 @@
   <sheetPr>
     <tabColor rgb="FF0E4F92"/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -651,251 +729,278 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="17"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
+      <c r="B2" s="15"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
+      <c r="B4" s="13"/>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="12"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B10" s="1" t="s">
+      <c r="B9" s="13"/>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="11" t="s">
+    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="12"/>
-    </row>
-    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="3">
+    </row>
+    <row r="15" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="13"/>
+    </row>
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B18" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="13"/>
+    </row>
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="3">
+      <c r="B21" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="3">
+      <c r="B25" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="8">
         <v>3</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="3">
+      <c r="B29" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B30" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="8">
         <v>4</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="3">
+      <c r="B33" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="8">
         <v>5</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="3">
+      <c r="B37" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="8">
         <v>6</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B37" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="3">
+      <c r="B41" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B42" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B43" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="8">
         <v>7</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B40" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B41" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" s="12"/>
-    </row>
-    <row r="44" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B44" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B45" s="4" t="s">
-        <v>33</v>
+      <c r="B45" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B46" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="11" t="s">
+      <c r="B46" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B48" s="12"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A49" s="5"/>
-      <c r="B49" s="1" t="s">
+    </row>
+    <row r="47" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B47" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A50" s="6"/>
-      <c r="B50" s="1" t="s">
+    <row r="49" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A51" s="7"/>
-      <c r="B51" s="1" t="s">
+      <c r="B49" s="13"/>
+    </row>
+    <row r="50" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B50" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A52" s="2"/>
-      <c r="B52" s="1" t="s">
+    <row r="51" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B51" s="5" t="s">
         <v>39</v>
       </c>
     </row>
+    <row r="52" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B52" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" s="13"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A55" s="9"/>
+      <c r="B55" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A56" s="10"/>
+      <c r="B56" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A57" s="11"/>
+      <c r="B57" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A58" s="6"/>
+      <c r="B58" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A49:B49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -916,114 +1021,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
+      <c r="A2" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="4" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
+      <c r="A4" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="9">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="3">
         <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="9">
+      <c r="A6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="3">
         <v>145</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>45</v>
+      <c r="C6" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="9">
+      <c r="A7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="3">
         <v>80</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>47</v>
+      <c r="C7" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="9">
+      <c r="A8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="3">
         <v>6500</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A11" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="10">
+      <c r="A10" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="4">
         <f>(B5-B6)*B7-B8</f>
         <v>1820</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>51</v>
+      <c r="C11" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
+      <c r="A13" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/examples/demos/05_simulation_and_charts.xlsx
+++ b/examples/demos/05_simulation_and_charts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B692E3D-04C6-4A84-8C36-25555FFAC609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D374528F-905F-47FF-BCD5-F4524413EA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -400,14 +400,14 @@
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -729,22 +729,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="13"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="17"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="13"/>
+      <c r="B4" s="15"/>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="5" t="s">
@@ -762,10 +762,10 @@
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="13"/>
+      <c r="B9" s="15"/>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="5" t="s">
@@ -788,10 +788,10 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="13"/>
+      <c r="B15" s="15"/>
     </row>
     <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
@@ -809,10 +809,10 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="13"/>
+      <c r="B20" s="15"/>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="8">
@@ -941,10 +941,10 @@
       </c>
     </row>
     <row r="49" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="13"/>
+      <c r="B49" s="15"/>
     </row>
     <row r="50" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="5" t="s">
@@ -962,10 +962,10 @@
       </c>
     </row>
     <row r="54" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B54" s="13"/>
+      <c r="B54" s="15"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A55" s="9"/>
@@ -993,14 +993,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A49:B49"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A49:B49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1024,37 +1024,37 @@
       <c r="A1" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
     </row>
     <row r="4" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
@@ -1098,13 +1098,13 @@
       <c r="A10" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2" t="s">
@@ -1122,13 +1122,13 @@
       <c r="A13" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/examples/demos/05_simulation_and_charts.xlsx
+++ b/examples/demos/05_simulation_and_charts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D374528F-905F-47FF-BCD5-F4524413EA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63A649B-0C5B-4B50-B791-F966F2ADD3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -400,12 +400,12 @@
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -729,10 +729,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="15"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="16" t="s">
@@ -741,10 +741,10 @@
       <c r="B2" s="17"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="15"/>
+      <c r="B4" s="13"/>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="5" t="s">
@@ -762,10 +762,10 @@
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="15"/>
+      <c r="B9" s="13"/>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="5" t="s">
@@ -788,10 +788,10 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="15"/>
+      <c r="B15" s="13"/>
     </row>
     <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
@@ -809,10 +809,10 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="15"/>
+      <c r="B20" s="13"/>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="8">
@@ -941,10 +941,10 @@
       </c>
     </row>
     <row r="49" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="15"/>
+      <c r="B49" s="13"/>
     </row>
     <row r="50" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="5" t="s">
@@ -962,10 +962,10 @@
       </c>
     </row>
     <row r="54" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B54" s="15"/>
+      <c r="B54" s="13"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A55" s="9"/>
